--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7160"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6560"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Users" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="314">
   <si>
     <t>SrNo</t>
   </si>
@@ -70,16 +70,16 @@
     <t>sultan@102</t>
   </si>
   <si>
-    <t>CHECKIN_OK</t>
-  </si>
-  <si>
-    <t>CHECKIN_DONE</t>
+    <t>CHECKOUT_OK</t>
+  </si>
+  <si>
+    <t>CHECKOUT_DONE</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-08-07 07:06:41</t>
+    <t>2026-08-18 13:24:18</t>
   </si>
   <si>
     <t>ASIAN WALA</t>
@@ -94,22 +94,7 @@
     <t>Hyphanet1%</t>
   </si>
   <si>
-    <t>2026-08-07 07:07:01</t>
-  </si>
-  <si>
-    <t>BHAGTANWALA</t>
-  </si>
-  <si>
-    <t>Nazir Ahmad</t>
-  </si>
-  <si>
-    <t>13714_19664_OR</t>
-  </si>
-  <si>
-    <t>Asdf@1122</t>
-  </si>
-  <si>
-    <t>2026-08-07 07:07:23</t>
+    <t>2026-08-18 13:24:38</t>
   </si>
   <si>
     <t>CHAK # 100 SB</t>
@@ -124,7 +109,7 @@
     <t>ahmad@786</t>
   </si>
   <si>
-    <t>2026-08-07 07:07:44</t>
+    <t>2026-08-18 13:24:59</t>
   </si>
   <si>
     <t>CHAK # 104 NB</t>
@@ -139,9 +124,6 @@
     <t>Hassan@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:08:02</t>
-  </si>
-  <si>
     <t>CHAK # 104 SB</t>
   </si>
   <si>
@@ -154,9 +136,6 @@
     <t>malik@506691</t>
   </si>
   <si>
-    <t>2026-08-07 07:08:18</t>
-  </si>
-  <si>
     <t>CHAK # 109 SB</t>
   </si>
   <si>
@@ -169,9 +148,6 @@
     <t>Shamas@456</t>
   </si>
   <si>
-    <t>2026-08-07 07:08:35</t>
-  </si>
-  <si>
     <t>CHAK # 113 SB</t>
   </si>
   <si>
@@ -184,9 +160,6 @@
     <t>@Zobi7172</t>
   </si>
   <si>
-    <t>2026-08-07 07:08:51</t>
-  </si>
-  <si>
     <t>RANA ZOHAIB ALI</t>
   </si>
   <si>
@@ -196,9 +169,6 @@
     <t>zzzzz@45</t>
   </si>
   <si>
-    <t>2026-08-07 07:09:09</t>
-  </si>
-  <si>
     <t>CHAK # 33 SB</t>
   </si>
   <si>
@@ -211,9 +181,6 @@
     <t>Abcd@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:09:27</t>
-  </si>
-  <si>
     <t>CHAK # 34 SB</t>
   </si>
   <si>
@@ -226,9 +193,6 @@
     <t>N@343434</t>
   </si>
   <si>
-    <t>2026-08-07 07:09:43</t>
-  </si>
-  <si>
     <t>CHAK # 36 NB</t>
   </si>
   <si>
@@ -241,9 +205,6 @@
     <t>Haseeeb@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:10:00</t>
-  </si>
-  <si>
     <t>CHAK # 36 SB</t>
   </si>
   <si>
@@ -256,9 +217,6 @@
     <t>Raza@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:10:18</t>
-  </si>
-  <si>
     <t>CHAK # 40 NB</t>
   </si>
   <si>
@@ -271,9 +229,6 @@
     <t>Farazkalyar@75</t>
   </si>
   <si>
-    <t>2026-08-07 07:10:35</t>
-  </si>
-  <si>
     <t>CHAK # 40 SB</t>
   </si>
   <si>
@@ -286,9 +241,6 @@
     <t>M@0302065</t>
   </si>
   <si>
-    <t>2026-08-07 07:10:52</t>
-  </si>
-  <si>
     <t>CHAK # 45 SB</t>
   </si>
   <si>
@@ -301,9 +253,6 @@
     <t>Ghulam@2</t>
   </si>
   <si>
-    <t>2026-08-07 07:11:11</t>
-  </si>
-  <si>
     <t>CHAK # 46 SB</t>
   </si>
   <si>
@@ -316,9 +265,6 @@
     <t>Javed@112</t>
   </si>
   <si>
-    <t>2026-08-07 07:11:28</t>
-  </si>
-  <si>
     <t>CHAK # 52 SB</t>
   </si>
   <si>
@@ -331,9 +277,6 @@
     <t>H@864545</t>
   </si>
   <si>
-    <t>2026-08-07 07:11:44</t>
-  </si>
-  <si>
     <t>Gulam Mustafa Tabassam</t>
   </si>
   <si>
@@ -343,9 +286,6 @@
     <t>Rana@124</t>
   </si>
   <si>
-    <t>2026-08-07 07:12:02</t>
-  </si>
-  <si>
     <t>CHAK # 58 NB</t>
   </si>
   <si>
@@ -358,9 +298,6 @@
     <t>s7043855@</t>
   </si>
   <si>
-    <t>2026-08-07 07:12:19</t>
-  </si>
-  <si>
     <t>CHAK # 67 A NB</t>
   </si>
   <si>
@@ -373,9 +310,6 @@
     <t>Adil@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:12:35</t>
-  </si>
-  <si>
     <t>CHAK # 70 SB</t>
   </si>
   <si>
@@ -388,9 +322,6 @@
     <t>Muda@13456</t>
   </si>
   <si>
-    <t>2026-08-07 07:12:56</t>
-  </si>
-  <si>
     <t>CHAK # 71 NB</t>
   </si>
   <si>
@@ -403,9 +334,6 @@
     <t>USMAN71NB+</t>
   </si>
   <si>
-    <t>2026-08-07 07:13:14</t>
-  </si>
-  <si>
     <t>CHAK # 74 SB</t>
   </si>
   <si>
@@ -418,9 +346,6 @@
     <t>Ali@786</t>
   </si>
   <si>
-    <t>2026-08-07 07:13:29</t>
-  </si>
-  <si>
     <t>CHAK # 84 SB</t>
   </si>
   <si>
@@ -433,9 +358,6 @@
     <t>Muhammadali@786</t>
   </si>
   <si>
-    <t>2026-08-07 07:13:46</t>
-  </si>
-  <si>
     <t>CHAK # 88 SB</t>
   </si>
   <si>
@@ -448,9 +370,6 @@
     <t>MShafi@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:14:04</t>
-  </si>
-  <si>
     <t>CHAK # 90 NB</t>
   </si>
   <si>
@@ -463,9 +382,6 @@
     <t>Salman@111</t>
   </si>
   <si>
-    <t>2026-08-07 07:14:21</t>
-  </si>
-  <si>
     <t>Kashif Ali</t>
   </si>
   <si>
@@ -475,9 +391,6 @@
     <t>654321@K</t>
   </si>
   <si>
-    <t>2026-08-07 07:14:37</t>
-  </si>
-  <si>
     <t>CHAK # 92 NB</t>
   </si>
   <si>
@@ -490,9 +403,6 @@
     <t>Azhar@13</t>
   </si>
   <si>
-    <t>2026-08-07 07:14:54</t>
-  </si>
-  <si>
     <t>CHAK # 96 SB</t>
   </si>
   <si>
@@ -505,9 +415,6 @@
     <t>MSajad@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:15:10</t>
-  </si>
-  <si>
     <t>CHAK # 97 NB</t>
   </si>
   <si>
@@ -520,9 +427,6 @@
     <t>12345H@</t>
   </si>
   <si>
-    <t>2026-08-07 07:15:28</t>
-  </si>
-  <si>
     <t>CHOKERA</t>
   </si>
   <si>
@@ -535,9 +439,6 @@
     <t>zaid@5</t>
   </si>
   <si>
-    <t>2026-08-07 07:15:46</t>
-  </si>
-  <si>
     <t>DHAREMA</t>
   </si>
   <si>
@@ -550,9 +451,6 @@
     <t>amanullah@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:16:03</t>
-  </si>
-  <si>
     <t>HAIDER ABAD TOWN</t>
   </si>
   <si>
@@ -562,9 +460,6 @@
     <t>naeem@6477</t>
   </si>
   <si>
-    <t>2026-08-07 07:16:19</t>
-  </si>
-  <si>
     <t>KHIZAR ABAD</t>
   </si>
   <si>
@@ -577,9 +472,6 @@
     <t>maharmuzamal6@</t>
   </si>
   <si>
-    <t>2026-08-07 07:16:36</t>
-  </si>
-  <si>
     <t>KOLO WAL</t>
   </si>
   <si>
@@ -592,9 +484,6 @@
     <t>Meesam@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:16:53</t>
-  </si>
-  <si>
     <t>LALLU WALI</t>
   </si>
   <si>
@@ -607,9 +496,6 @@
     <t>M@1969422</t>
   </si>
   <si>
-    <t>2026-08-07 07:17:10</t>
-  </si>
-  <si>
     <t>LUDAY WALA</t>
   </si>
   <si>
@@ -622,9 +508,6 @@
     <t>Masood@111</t>
   </si>
   <si>
-    <t>2026-08-07 07:17:26</t>
-  </si>
-  <si>
     <t>LUQMAN</t>
   </si>
   <si>
@@ -637,9 +520,6 @@
     <t>gy@#_huiad$3/</t>
   </si>
   <si>
-    <t>2026-08-07 07:17:42</t>
-  </si>
-  <si>
     <t>MARI</t>
   </si>
   <si>
@@ -652,9 +532,6 @@
     <t>faisal@1577</t>
   </si>
   <si>
-    <t>2026-08-07 07:17:58</t>
-  </si>
-  <si>
     <t>MITHA LAK</t>
   </si>
   <si>
@@ -667,9 +544,6 @@
     <t>Umair@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:18:13</t>
-  </si>
-  <si>
     <t>REMOUNT DEPOT</t>
   </si>
   <si>
@@ -682,9 +556,6 @@
     <t>Satar@234</t>
   </si>
   <si>
-    <t>2026-08-07 07:18:29</t>
-  </si>
-  <si>
     <t>SKESAR</t>
   </si>
   <si>
@@ -697,9 +568,6 @@
     <t>mahar@2618</t>
   </si>
   <si>
-    <t>2026-08-07 07:18:45</t>
-  </si>
-  <si>
     <t>UC 140/1</t>
   </si>
   <si>
@@ -712,9 +580,6 @@
     <t>Usman140+</t>
   </si>
   <si>
-    <t>2026-08-07 07:19:00</t>
-  </si>
-  <si>
     <t>UC 141/2</t>
   </si>
   <si>
@@ -727,9 +592,6 @@
     <t>Usama118+</t>
   </si>
   <si>
-    <t>2026-08-07 07:19:16</t>
-  </si>
-  <si>
     <t>UC 142/3</t>
   </si>
   <si>
@@ -742,9 +604,6 @@
     <t>@HARAM11</t>
   </si>
   <si>
-    <t>2026-08-07 07:19:33</t>
-  </si>
-  <si>
     <t>UC 143/4</t>
   </si>
   <si>
@@ -757,9 +616,6 @@
     <t>AR@123456</t>
   </si>
   <si>
-    <t>2026-08-07 07:19:48</t>
-  </si>
-  <si>
     <t>UC 145/6</t>
   </si>
   <si>
@@ -772,9 +628,6 @@
     <t>Health@145</t>
   </si>
   <si>
-    <t>2026-08-07 07:20:04</t>
-  </si>
-  <si>
     <t>UC 146/7</t>
   </si>
   <si>
@@ -787,9 +640,6 @@
     <t>Aiman@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:20:22</t>
-  </si>
-  <si>
     <t>UC 147/8</t>
   </si>
   <si>
@@ -802,9 +652,6 @@
     <t>Israr147@</t>
   </si>
   <si>
-    <t>2026-08-07 07:20:37</t>
-  </si>
-  <si>
     <t>UC 148/9</t>
   </si>
   <si>
@@ -817,9 +664,6 @@
     <t>mmw@2345</t>
   </si>
   <si>
-    <t>2026-08-07 07:20:53</t>
-  </si>
-  <si>
     <t>UC 149/10</t>
   </si>
   <si>
@@ -832,9 +676,6 @@
     <t>Nazia@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:21:09</t>
-  </si>
-  <si>
     <t>UC 150/11</t>
   </si>
   <si>
@@ -847,9 +688,6 @@
     <t>Health@150</t>
   </si>
   <si>
-    <t>2026-08-07 07:21:24</t>
-  </si>
-  <si>
     <t>UC 151/12</t>
   </si>
   <si>
@@ -862,9 +700,6 @@
     <t>Riaz@791</t>
   </si>
   <si>
-    <t>2026-08-07 07:21:41</t>
-  </si>
-  <si>
     <t>UC 152/13</t>
   </si>
   <si>
@@ -877,9 +712,6 @@
     <t>Akhtar@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:21:57</t>
-  </si>
-  <si>
     <t>UC 153/14</t>
   </si>
   <si>
@@ -892,9 +724,6 @@
     <t>SaHista@12</t>
   </si>
   <si>
-    <t>2026-08-07 07:22:11</t>
-  </si>
-  <si>
     <t>UC 154/15</t>
   </si>
   <si>
@@ -907,9 +736,6 @@
     <t>Huda154@</t>
   </si>
   <si>
-    <t>2026-08-07 07:22:26</t>
-  </si>
-  <si>
     <t>UC 155/16</t>
   </si>
   <si>
@@ -922,9 +748,6 @@
     <t>NOmiii@134</t>
   </si>
   <si>
-    <t>2026-08-07 07:22:43</t>
-  </si>
-  <si>
     <t>UC 156/17</t>
   </si>
   <si>
@@ -937,9 +760,6 @@
     <t>@zain_156</t>
   </si>
   <si>
-    <t>2026-08-07 07:22:58</t>
-  </si>
-  <si>
     <t>UC 157/18</t>
   </si>
   <si>
@@ -952,9 +772,6 @@
     <t>@Younas123</t>
   </si>
   <si>
-    <t>2026-08-07 07:23:14</t>
-  </si>
-  <si>
     <t>UC 158/19</t>
   </si>
   <si>
@@ -964,9 +781,6 @@
     <t>15072_19713_OR</t>
   </si>
   <si>
-    <t>2026-08-07 07:23:30</t>
-  </si>
-  <si>
     <t>Muhammad Ishfaq</t>
   </si>
   <si>
@@ -976,9 +790,6 @@
     <t>Ishfaq158@</t>
   </si>
   <si>
-    <t>2026-08-07 07:23:45</t>
-  </si>
-  <si>
     <t>UC 159/20</t>
   </si>
   <si>
@@ -991,9 +802,6 @@
     <t>ArifQ@12345</t>
   </si>
   <si>
-    <t>2026-08-07 07:24:00</t>
-  </si>
-  <si>
     <t>UC 160/21</t>
   </si>
   <si>
@@ -1006,9 +814,6 @@
     <t>salahuddeen@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:24:15</t>
-  </si>
-  <si>
     <t>UC 161/22</t>
   </si>
   <si>
@@ -1021,9 +826,6 @@
     <t>161union@</t>
   </si>
   <si>
-    <t>2026-08-07 07:24:30</t>
-  </si>
-  <si>
     <t>UC 162/23 CANTT # 1</t>
   </si>
   <si>
@@ -1036,9 +838,6 @@
     <t>Saif162@</t>
   </si>
   <si>
-    <t>2026-08-07 07:24:46</t>
-  </si>
-  <si>
     <t>UC 163/24 CANTT # 2</t>
   </si>
   <si>
@@ -1051,9 +850,6 @@
     <t>Muhammad123@</t>
   </si>
   <si>
-    <t>2026-08-07 07:25:01</t>
-  </si>
-  <si>
     <t>UC 164/25 CANTT # 3</t>
   </si>
   <si>
@@ -1066,9 +862,6 @@
     <t>Nouman1+</t>
   </si>
   <si>
-    <t>2026-08-07 07:25:16</t>
-  </si>
-  <si>
     <t>Gull Zubair</t>
   </si>
   <si>
@@ -1078,9 +871,6 @@
     <t>Zubair@123</t>
   </si>
   <si>
-    <t>2026-08-07 07:25:33</t>
-  </si>
-  <si>
     <t>UC 165/26 CANTT # 4</t>
   </si>
   <si>
@@ -1093,9 +883,6 @@
     <t>abid@555</t>
   </si>
   <si>
-    <t>2026-08-07 07:25:49</t>
-  </si>
-  <si>
     <t>UC 166/27 CANTT # 5</t>
   </si>
   <si>
@@ -1105,9 +892,6 @@
     <t>Azhar@12345</t>
   </si>
   <si>
-    <t>2026-08-07 07:26:34</t>
-  </si>
-  <si>
     <t>UC 167/28 CANTT # 6</t>
   </si>
   <si>
@@ -1120,9 +904,6 @@
     <t>@234Islam</t>
   </si>
   <si>
-    <t>2026-08-07 07:26:50</t>
-  </si>
-  <si>
     <t>Usama Ali</t>
   </si>
   <si>
@@ -1132,9 +913,6 @@
     <t>usama1+</t>
   </si>
   <si>
-    <t>2026-08-07 07:27:06</t>
-  </si>
-  <si>
     <t>Qurat-ul-Ain</t>
   </si>
   <si>
@@ -1144,9 +922,6 @@
     <t>Qurat@1122</t>
   </si>
   <si>
-    <t>2026-08-07 07:27:22</t>
-  </si>
-  <si>
     <t>Muhammad Faseeh Ullah</t>
   </si>
   <si>
@@ -1156,9 +931,6 @@
     <t>Faseeh153@</t>
   </si>
   <si>
-    <t>2026-08-07 07:27:38</t>
-  </si>
-  <si>
     <t>Abdul Wahab</t>
   </si>
   <si>
@@ -1168,7 +940,25 @@
     <t>Wahab@1122</t>
   </si>
   <si>
-    <t>2026-08-07 07:27:54</t>
+    <t>Rimsha</t>
+  </si>
+  <si>
+    <t>7185_19707_OR</t>
+  </si>
+  <si>
+    <t>@Rimsha786</t>
+  </si>
+  <si>
+    <t>Uc-106/Asianwala</t>
+  </si>
+  <si>
+    <t>Muhammad Rizwan</t>
+  </si>
+  <si>
+    <t>14011_19807_OR</t>
+  </si>
+  <si>
+    <t>Shahdat@2021</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1349,6 +1139,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1848,16 +1639,16 @@
         <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>19</v>
@@ -1874,28 +1665,28 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>19</v>
@@ -1912,28 +1703,28 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>19</v>
@@ -1950,28 +1741,28 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>19</v>
@@ -1988,28 +1779,28 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>19</v>
@@ -2026,28 +1817,28 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>19</v>
@@ -2064,28 +1855,28 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>19</v>
@@ -2102,28 +1893,28 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -2140,28 +1931,28 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>19</v>
@@ -2178,28 +1969,28 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>19</v>
@@ -2216,28 +2007,28 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>19</v>
@@ -2254,28 +2045,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>19</v>
@@ -2292,28 +2083,28 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>19</v>
@@ -2330,28 +2121,28 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>19</v>
@@ -2368,28 +2159,28 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>19</v>
@@ -2406,28 +2197,28 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>108</v>
+        <v>19</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>19</v>
@@ -2444,28 +2235,28 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>19</v>
@@ -2482,28 +2273,28 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>118</v>
+        <v>19</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>19</v>
@@ -2520,28 +2311,28 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>123</v>
+        <v>19</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>19</v>
@@ -2558,28 +2349,28 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>128</v>
+        <v>19</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>19</v>
@@ -2596,28 +2387,28 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>133</v>
+        <v>19</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>19</v>
@@ -2634,28 +2425,28 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>19</v>
@@ -2672,28 +2463,28 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>143</v>
+        <v>19</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>19</v>
@@ -2710,28 +2501,28 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>19</v>
@@ -2748,28 +2539,28 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>19</v>
@@ -2786,28 +2577,28 @@
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>157</v>
+        <v>19</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>19</v>
@@ -2824,28 +2615,28 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>160</v>
+        <v>134</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>161</v>
+        <v>135</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>162</v>
+        <v>19</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>19</v>
@@ -2862,28 +2653,28 @@
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>19</v>
@@ -2900,28 +2691,28 @@
         <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>168</v>
+        <v>140</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>171</v>
+        <v>143</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>172</v>
+        <v>19</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>19</v>
@@ -2938,28 +2729,28 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>19</v>
@@ -2976,28 +2767,28 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>32</v>
+        <v>148</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>19</v>
@@ -3014,28 +2805,28 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>185</v>
+        <v>154</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>186</v>
+        <v>19</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>19</v>
@@ -3052,28 +2843,28 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>190</v>
+        <v>158</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>19</v>
@@ -3090,28 +2881,28 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>19</v>
@@ -3128,28 +2919,28 @@
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>201</v>
+        <v>19</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>19</v>
@@ -3166,28 +2957,28 @@
         <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>204</v>
+        <v>169</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>206</v>
+        <v>19</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>19</v>
@@ -3204,28 +2995,28 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>207</v>
+        <v>171</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>208</v>
+        <v>172</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>209</v>
+        <v>173</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>210</v>
+        <v>174</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>211</v>
+        <v>19</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>19</v>
@@ -3242,28 +3033,28 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>212</v>
+        <v>175</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>213</v>
+        <v>176</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>214</v>
+        <v>177</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>215</v>
+        <v>178</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>216</v>
+        <v>19</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>19</v>
@@ -3280,28 +3071,28 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>221</v>
+        <v>19</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>19</v>
@@ -3318,28 +3109,28 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>225</v>
+        <v>186</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>19</v>
@@ -3356,28 +3147,28 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>231</v>
+        <v>19</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>19</v>
@@ -3394,28 +3185,28 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>233</v>
+        <v>192</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>235</v>
+        <v>194</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>236</v>
+        <v>19</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>19</v>
@@ -3432,28 +3223,28 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>237</v>
+        <v>195</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>240</v>
+        <v>198</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>241</v>
+        <v>19</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>19</v>
@@ -3470,28 +3261,28 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>242</v>
+        <v>199</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>243</v>
+        <v>200</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>244</v>
+        <v>201</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>19</v>
@@ -3508,28 +3299,28 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>247</v>
+        <v>203</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>249</v>
+        <v>205</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>250</v>
+        <v>206</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>251</v>
+        <v>19</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>19</v>
@@ -3546,28 +3337,28 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>252</v>
+        <v>207</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>253</v>
+        <v>208</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>254</v>
+        <v>209</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>255</v>
+        <v>210</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>19</v>
@@ -3584,28 +3375,28 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>257</v>
+        <v>211</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>258</v>
+        <v>212</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>259</v>
+        <v>213</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>260</v>
+        <v>214</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>261</v>
+        <v>19</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>19</v>
@@ -3622,28 +3413,28 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>262</v>
+        <v>215</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>263</v>
+        <v>216</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>264</v>
+        <v>217</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>265</v>
+        <v>218</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>266</v>
+        <v>19</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>19</v>
@@ -3660,28 +3451,28 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>267</v>
+        <v>219</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>268</v>
+        <v>220</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>269</v>
+        <v>221</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>270</v>
+        <v>222</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>19</v>
@@ -3698,28 +3489,28 @@
         <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>276</v>
+        <v>19</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>19</v>
@@ -3736,28 +3527,28 @@
         <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>277</v>
+        <v>227</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>278</v>
+        <v>228</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>279</v>
+        <v>229</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>281</v>
+        <v>19</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>19</v>
@@ -3774,28 +3565,28 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>283</v>
+        <v>232</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>284</v>
+        <v>233</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>286</v>
+        <v>19</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>19</v>
@@ -3812,28 +3603,28 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>289</v>
+        <v>237</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>291</v>
+        <v>19</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>19</v>
@@ -3850,28 +3641,28 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>294</v>
+        <v>241</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>295</v>
+        <v>242</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>296</v>
+        <v>19</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>19</v>
@@ -3888,28 +3679,28 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>297</v>
+        <v>243</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>298</v>
+        <v>244</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>300</v>
+        <v>246</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>301</v>
+        <v>19</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>19</v>
@@ -3926,28 +3717,28 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>302</v>
+        <v>247</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>303</v>
+        <v>248</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>304</v>
+        <v>249</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>305</v>
+        <v>250</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>306</v>
+        <v>19</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>19</v>
@@ -3964,28 +3755,28 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>310</v>
+        <v>222</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>311</v>
+        <v>19</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>19</v>
@@ -4002,28 +3793,28 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>314</v>
+        <v>255</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>315</v>
+        <v>19</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>19</v>
@@ -4040,28 +3831,28 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>312</v>
+        <v>257</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>316</v>
+        <v>258</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>317</v>
+        <v>259</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>319</v>
+        <v>19</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>19</v>
@@ -4078,28 +3869,28 @@
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>320</v>
+        <v>261</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>321</v>
+        <v>262</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>322</v>
+        <v>263</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>323</v>
+        <v>264</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>19</v>
@@ -4116,28 +3907,28 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>325</v>
+        <v>265</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>328</v>
+        <v>268</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>329</v>
+        <v>19</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>19</v>
@@ -4154,28 +3945,28 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>330</v>
+        <v>269</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>331</v>
+        <v>270</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>332</v>
+        <v>271</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>333</v>
+        <v>272</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>334</v>
+        <v>19</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>19</v>
@@ -4192,28 +3983,28 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>335</v>
+        <v>273</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>336</v>
+        <v>274</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>337</v>
+        <v>275</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>338</v>
+        <v>276</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>339</v>
+        <v>19</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>19</v>
@@ -4230,28 +4021,28 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>340</v>
+        <v>277</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>341</v>
+        <v>278</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>342</v>
+        <v>279</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>344</v>
+        <v>19</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>19</v>
@@ -4268,28 +4059,28 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>345</v>
+        <v>277</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>346</v>
+        <v>281</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>347</v>
+        <v>282</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>348</v>
+        <v>283</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>19</v>
@@ -4306,28 +4097,28 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>345</v>
+        <v>284</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>350</v>
+        <v>285</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>351</v>
+        <v>286</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>352</v>
+        <v>287</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>19</v>
@@ -4344,28 +4135,28 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>355</v>
+        <v>125</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>356</v>
+        <v>289</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>357</v>
+        <v>290</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>19</v>
@@ -4382,28 +4173,28 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>359</v>
+        <v>291</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>154</v>
+        <v>292</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>360</v>
+        <v>293</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>361</v>
+        <v>294</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>362</v>
+        <v>19</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>19</v>
@@ -4420,28 +4211,28 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>363</v>
+        <v>215</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>364</v>
+        <v>295</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>367</v>
+        <v>19</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>19</v>
@@ -4457,29 +4248,29 @@
       <c r="C74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D74" s="2" t="s">
-        <v>267</v>
+      <c r="D74" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>370</v>
+        <v>299</v>
+      </c>
+      <c r="G74" s="4" t="s">
+        <v>300</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>371</v>
+        <v>19</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>19</v>
@@ -4496,28 +4287,28 @@
         <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>372</v>
+        <v>301</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>373</v>
+        <v>302</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>374</v>
+        <v>303</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>375</v>
+        <v>19</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>19</v>
@@ -4534,28 +4325,28 @@
         <v>12</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>378</v>
+        <v>227</v>
+      </c>
+      <c r="E76" t="s">
+        <v>304</v>
+      </c>
+      <c r="F76" t="s">
+        <v>305</v>
+      </c>
+      <c r="G76" t="s">
+        <v>306</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>379</v>
+        <v>19</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>19</v>
@@ -4571,29 +4362,26 @@
       <c r="C77" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>282</v>
-      </c>
       <c r="E77" t="s">
-        <v>380</v>
+        <v>307</v>
       </c>
       <c r="F77" t="s">
-        <v>381</v>
+        <v>308</v>
       </c>
       <c r="G77" t="s">
-        <v>382</v>
+        <v>309</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>383</v>
+        <v>19</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>19</v>
@@ -4609,7 +4397,19 @@
       <c r="C78" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H78" s="5" t="s">
+      <c r="D78" t="s">
+        <v>310</v>
+      </c>
+      <c r="E78" t="s">
+        <v>311</v>
+      </c>
+      <c r="F78" t="s">
+        <v>312</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>19</v>
       </c>
       <c r="I78" t="s">
@@ -4639,9 +4439,9 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+      <c r="J80" s="8"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
@@ -4649,14 +4449,15 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-      <c r="H81" s="8"/>
-      <c r="I81" s="9"/>
+      <c r="H81" s="9"/>
+      <c r="I81" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:L81"/>
   <hyperlinks>
-    <hyperlink ref="G75" r:id="rId1"/>
-    <hyperlink ref="G76" r:id="rId2"/>
+    <hyperlink ref="G74" r:id="rId1"/>
+    <hyperlink ref="G75" r:id="rId2"/>
+    <hyperlink ref="G78" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="328">
   <si>
     <t>SrNo</t>
   </si>
@@ -79,7 +79,7 @@
     <t/>
   </si>
   <si>
-    <t>2026-08-18 13:24:18</t>
+    <t>2026-08-20 14:03:03</t>
   </si>
   <si>
     <t>ASIAN WALA</t>
@@ -94,7 +94,7 @@
     <t>Hyphanet1%</t>
   </si>
   <si>
-    <t>2026-08-18 13:24:38</t>
+    <t>2026-08-20 14:03:25</t>
   </si>
   <si>
     <t>CHAK # 100 SB</t>
@@ -109,7 +109,7 @@
     <t>ahmad@786</t>
   </si>
   <si>
-    <t>2026-08-18 13:24:59</t>
+    <t>2026-08-20 14:03:42</t>
   </si>
   <si>
     <t>CHAK # 104 NB</t>
@@ -124,6 +124,9 @@
     <t>Hassan@123</t>
   </si>
   <si>
+    <t>2026-08-20 14:04:00</t>
+  </si>
+  <si>
     <t>CHAK # 104 SB</t>
   </si>
   <si>
@@ -136,6 +139,9 @@
     <t>malik@506691</t>
   </si>
   <si>
+    <t>2026-08-20 14:04:15</t>
+  </si>
+  <si>
     <t>CHAK # 109 SB</t>
   </si>
   <si>
@@ -148,6 +154,9 @@
     <t>Shamas@456</t>
   </si>
   <si>
+    <t>2026-08-20 14:04:31</t>
+  </si>
+  <si>
     <t>CHAK # 113 SB</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
     <t>@Zobi7172</t>
   </si>
   <si>
+    <t>2026-08-20 14:04:46</t>
+  </si>
+  <si>
     <t>RANA ZOHAIB ALI</t>
   </si>
   <si>
@@ -169,6 +181,9 @@
     <t>zzzzz@45</t>
   </si>
   <si>
+    <t>2026-08-20 14:05:03</t>
+  </si>
+  <si>
     <t>CHAK # 33 SB</t>
   </si>
   <si>
@@ -181,6 +196,9 @@
     <t>Abcd@123</t>
   </si>
   <si>
+    <t>2026-08-20 14:05:19</t>
+  </si>
+  <si>
     <t>CHAK # 34 SB</t>
   </si>
   <si>
@@ -193,6 +211,9 @@
     <t>N@343434</t>
   </si>
   <si>
+    <t>2026-08-20 14:05:36</t>
+  </si>
+  <si>
     <t>CHAK # 36 NB</t>
   </si>
   <si>
@@ -205,6 +226,9 @@
     <t>Haseeeb@123</t>
   </si>
   <si>
+    <t>2026-08-20 14:05:56</t>
+  </si>
+  <si>
     <t>CHAK # 36 SB</t>
   </si>
   <si>
@@ -217,6 +241,9 @@
     <t>Raza@123</t>
   </si>
   <si>
+    <t>2026-08-20 14:06:12</t>
+  </si>
+  <si>
     <t>CHAK # 40 NB</t>
   </si>
   <si>
@@ -229,6 +256,9 @@
     <t>Farazkalyar@75</t>
   </si>
   <si>
+    <t>2026-08-20 14:06:27</t>
+  </si>
+  <si>
     <t>CHAK # 40 SB</t>
   </si>
   <si>
@@ -241,6 +271,9 @@
     <t>M@0302065</t>
   </si>
   <si>
+    <t>2026-08-20 14:06:45</t>
+  </si>
+  <si>
     <t>CHAK # 45 SB</t>
   </si>
   <si>
@@ -253,6 +286,9 @@
     <t>Ghulam@2</t>
   </si>
   <si>
+    <t>2026-08-20 14:07:04</t>
+  </si>
+  <si>
     <t>CHAK # 46 SB</t>
   </si>
   <si>
@@ -265,6 +301,9 @@
     <t>Javed@112</t>
   </si>
   <si>
+    <t>2026-08-20 14:07:22</t>
+  </si>
+  <si>
     <t>CHAK # 52 SB</t>
   </si>
   <si>
@@ -275,6 +314,9 @@
   </si>
   <si>
     <t>H@864545</t>
+  </si>
+  <si>
+    <t>2026-08-20 14:07:38</t>
   </si>
   <si>
     <t>Gulam Mustafa Tabassam</t>
@@ -1639,16 +1681,16 @@
         <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>19</v>
@@ -1665,28 +1707,28 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>19</v>
@@ -1703,28 +1745,28 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>19</v>
@@ -1741,28 +1783,28 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>19</v>
@@ -1779,28 +1821,28 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>19</v>
@@ -1817,28 +1859,28 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>19</v>
@@ -1855,28 +1897,28 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>19</v>
@@ -1893,28 +1935,28 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -1931,28 +1973,28 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>19</v>
@@ -1969,28 +2011,28 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>19</v>
@@ -2007,28 +2049,28 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>19</v>
@@ -2045,28 +2087,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>19</v>
@@ -2083,28 +2125,28 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>19</v>
@@ -2121,28 +2163,28 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>19</v>
+        <v>99</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>19</v>
@@ -2159,16 +2201,16 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>19</v>
@@ -2197,16 +2239,16 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>19</v>
@@ -2235,16 +2277,16 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>19</v>
@@ -2273,16 +2315,16 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>19</v>
@@ -2311,16 +2353,16 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>19</v>
@@ -2349,16 +2391,16 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>19</v>
@@ -2387,16 +2429,16 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>19</v>
@@ -2425,16 +2467,16 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>19</v>
@@ -2463,16 +2505,16 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>19</v>
@@ -2501,16 +2543,16 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>19</v>
@@ -2539,16 +2581,16 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>19</v>
@@ -2577,16 +2619,16 @@
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>19</v>
@@ -2615,16 +2657,16 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>133</v>
+        <v>147</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>19</v>
@@ -2653,16 +2695,16 @@
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>19</v>
@@ -2691,16 +2733,16 @@
         <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>19</v>
@@ -2729,16 +2771,16 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>19</v>
@@ -2767,16 +2809,16 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>19</v>
@@ -2805,16 +2847,16 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>19</v>
@@ -2843,16 +2885,16 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>19</v>
@@ -2881,16 +2923,16 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>19</v>
@@ -2919,16 +2961,16 @@
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>19</v>
@@ -2957,16 +2999,16 @@
         <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>19</v>
@@ -2995,16 +3037,16 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>19</v>
@@ -3033,16 +3075,16 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>19</v>
@@ -3071,16 +3113,16 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>19</v>
@@ -3109,16 +3151,16 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>19</v>
@@ -3147,16 +3189,16 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>19</v>
@@ -3185,16 +3227,16 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>19</v>
@@ -3223,16 +3265,16 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>19</v>
@@ -3261,16 +3303,16 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>19</v>
@@ -3299,16 +3341,16 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>19</v>
@@ -3337,16 +3379,16 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>19</v>
@@ -3375,16 +3417,16 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>212</v>
+        <v>226</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>19</v>
@@ -3413,16 +3455,16 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>19</v>
@@ -3451,16 +3493,16 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>19</v>
@@ -3489,16 +3531,16 @@
         <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>19</v>
@@ -3527,16 +3569,16 @@
         <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>19</v>
@@ -3565,16 +3607,16 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>19</v>
@@ -3603,16 +3645,16 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>19</v>
@@ -3641,16 +3683,16 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>19</v>
@@ -3679,16 +3721,16 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>19</v>
@@ -3717,16 +3759,16 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>19</v>
@@ -3755,16 +3797,16 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>19</v>
@@ -3793,16 +3835,16 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>19</v>
@@ -3831,16 +3873,16 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>19</v>
@@ -3869,16 +3911,16 @@
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>263</v>
+        <v>277</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>19</v>
@@ -3907,16 +3949,16 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>19</v>
@@ -3945,16 +3987,16 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>19</v>
@@ -3983,16 +4025,16 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>19</v>
@@ -4021,16 +4063,16 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>19</v>
@@ -4059,16 +4101,16 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>19</v>
@@ -4097,16 +4139,16 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>19</v>
@@ -4135,16 +4177,16 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>19</v>
@@ -4173,16 +4215,16 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>19</v>
@@ -4211,16 +4253,16 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>19</v>
@@ -4249,16 +4291,16 @@
         <v>12</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>19</v>
@@ -4287,16 +4329,16 @@
         <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>19</v>
@@ -4325,16 +4367,16 @@
         <v>12</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="E76" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="F76" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="G76" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>19</v>
@@ -4363,13 +4405,13 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F77" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="G77" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>19</v>
@@ -4398,16 +4440,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="E78" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="F78" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>19</v>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="313">
   <si>
     <t>SrNo</t>
   </si>
@@ -70,16 +70,16 @@
     <t>sultan@102</t>
   </si>
   <si>
-    <t>CHECKOUT_OK</t>
-  </si>
-  <si>
-    <t>CHECKOUT_DONE</t>
+    <t>CHECKIN_OK</t>
+  </si>
+  <si>
+    <t>CHECKIN_DONE</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>2026-08-20 14:03:03</t>
+    <t>2026-08-21 07:02:11</t>
   </si>
   <si>
     <t>ASIAN WALA</t>
@@ -94,7 +94,7 @@
     <t>Hyphanet1%</t>
   </si>
   <si>
-    <t>2026-08-20 14:03:25</t>
+    <t>2026-08-21 07:02:30</t>
   </si>
   <si>
     <t>CHAK # 100 SB</t>
@@ -109,9 +109,6 @@
     <t>ahmad@786</t>
   </si>
   <si>
-    <t>2026-08-20 14:03:42</t>
-  </si>
-  <si>
     <t>CHAK # 104 NB</t>
   </si>
   <si>
@@ -124,9 +121,6 @@
     <t>Hassan@123</t>
   </si>
   <si>
-    <t>2026-08-20 14:04:00</t>
-  </si>
-  <si>
     <t>CHAK # 104 SB</t>
   </si>
   <si>
@@ -139,9 +133,6 @@
     <t>malik@506691</t>
   </si>
   <si>
-    <t>2026-08-20 14:04:15</t>
-  </si>
-  <si>
     <t>CHAK # 109 SB</t>
   </si>
   <si>
@@ -154,9 +145,6 @@
     <t>Shamas@456</t>
   </si>
   <si>
-    <t>2026-08-20 14:04:31</t>
-  </si>
-  <si>
     <t>CHAK # 113 SB</t>
   </si>
   <si>
@@ -169,9 +157,6 @@
     <t>@Zobi7172</t>
   </si>
   <si>
-    <t>2026-08-20 14:04:46</t>
-  </si>
-  <si>
     <t>RANA ZOHAIB ALI</t>
   </si>
   <si>
@@ -181,9 +166,6 @@
     <t>zzzzz@45</t>
   </si>
   <si>
-    <t>2026-08-20 14:05:03</t>
-  </si>
-  <si>
     <t>CHAK # 33 SB</t>
   </si>
   <si>
@@ -196,9 +178,6 @@
     <t>Abcd@123</t>
   </si>
   <si>
-    <t>2026-08-20 14:05:19</t>
-  </si>
-  <si>
     <t>CHAK # 34 SB</t>
   </si>
   <si>
@@ -211,9 +190,6 @@
     <t>N@343434</t>
   </si>
   <si>
-    <t>2026-08-20 14:05:36</t>
-  </si>
-  <si>
     <t>CHAK # 36 NB</t>
   </si>
   <si>
@@ -226,9 +202,6 @@
     <t>Haseeeb@123</t>
   </si>
   <si>
-    <t>2026-08-20 14:05:56</t>
-  </si>
-  <si>
     <t>CHAK # 36 SB</t>
   </si>
   <si>
@@ -241,9 +214,6 @@
     <t>Raza@123</t>
   </si>
   <si>
-    <t>2026-08-20 14:06:12</t>
-  </si>
-  <si>
     <t>CHAK # 40 NB</t>
   </si>
   <si>
@@ -256,9 +226,6 @@
     <t>Farazkalyar@75</t>
   </si>
   <si>
-    <t>2026-08-20 14:06:27</t>
-  </si>
-  <si>
     <t>CHAK # 40 SB</t>
   </si>
   <si>
@@ -271,9 +238,6 @@
     <t>M@0302065</t>
   </si>
   <si>
-    <t>2026-08-20 14:06:45</t>
-  </si>
-  <si>
     <t>CHAK # 45 SB</t>
   </si>
   <si>
@@ -286,9 +250,6 @@
     <t>Ghulam@2</t>
   </si>
   <si>
-    <t>2026-08-20 14:07:04</t>
-  </si>
-  <si>
     <t>CHAK # 46 SB</t>
   </si>
   <si>
@@ -301,9 +262,6 @@
     <t>Javed@112</t>
   </si>
   <si>
-    <t>2026-08-20 14:07:22</t>
-  </si>
-  <si>
     <t>CHAK # 52 SB</t>
   </si>
   <si>
@@ -314,9 +272,6 @@
   </si>
   <si>
     <t>H@864545</t>
-  </si>
-  <si>
-    <t>2026-08-20 14:07:38</t>
   </si>
   <si>
     <t>Gulam Mustafa Tabassam</t>
@@ -1643,16 +1598,16 @@
         <v>29</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>19</v>
@@ -1669,28 +1624,28 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>19</v>
@@ -1707,28 +1662,28 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>19</v>
@@ -1745,28 +1700,28 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>19</v>
@@ -1783,28 +1738,28 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>19</v>
@@ -1821,28 +1776,28 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>19</v>
@@ -1859,28 +1814,28 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>19</v>
@@ -1897,28 +1852,28 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>19</v>
@@ -1935,28 +1890,28 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>19</v>
@@ -1973,28 +1928,28 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>19</v>
@@ -2011,28 +1966,28 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>19</v>
@@ -2049,28 +2004,28 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>19</v>
@@ -2087,28 +2042,28 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>19</v>
@@ -2125,28 +2080,28 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>19</v>
@@ -2163,28 +2118,28 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>19</v>
@@ -2201,16 +2156,16 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>19</v>
@@ -2239,16 +2194,16 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>19</v>
@@ -2277,16 +2232,16 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>19</v>
@@ -2315,16 +2270,16 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>19</v>
@@ -2353,16 +2308,16 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>19</v>
@@ -2391,16 +2346,16 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>19</v>
@@ -2429,16 +2384,16 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>19</v>
@@ -2467,16 +2422,16 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>19</v>
@@ -2505,16 +2460,16 @@
         <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>19</v>
@@ -2543,16 +2498,16 @@
         <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>19</v>
@@ -2581,16 +2536,16 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>19</v>
@@ -2619,16 +2574,16 @@
         <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>19</v>
@@ -2657,16 +2612,16 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>19</v>
@@ -2695,16 +2650,16 @@
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>19</v>
@@ -2733,16 +2688,16 @@
         <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>19</v>
@@ -2771,16 +2726,16 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>19</v>
@@ -2809,16 +2764,16 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>19</v>
@@ -2847,16 +2802,16 @@
         <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>19</v>
@@ -2885,16 +2840,16 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>19</v>
@@ -2923,16 +2878,16 @@
         <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>19</v>
@@ -2961,16 +2916,16 @@
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>19</v>
@@ -2999,16 +2954,16 @@
         <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>19</v>
@@ -3037,16 +2992,16 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>19</v>
@@ -3075,16 +3030,16 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>19</v>
@@ -3113,16 +3068,16 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>19</v>
@@ -3151,16 +3106,16 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>19</v>
@@ -3189,16 +3144,16 @@
         <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>19</v>
@@ -3227,16 +3182,16 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>19</v>
@@ -3265,16 +3220,16 @@
         <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>19</v>
@@ -3303,16 +3258,16 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>19</v>
@@ -3341,16 +3296,16 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>19</v>
@@ -3379,16 +3334,16 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>19</v>
@@ -3417,16 +3372,16 @@
         <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>19</v>
@@ -3455,16 +3410,16 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>19</v>
@@ -3493,16 +3448,16 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>19</v>
@@ -3531,16 +3486,16 @@
         <v>12</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>19</v>
@@ -3569,16 +3524,16 @@
         <v>12</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>19</v>
@@ -3607,16 +3562,16 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>19</v>
@@ -3645,16 +3600,16 @@
         <v>12</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>19</v>
@@ -3683,16 +3638,16 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>19</v>
@@ -3721,16 +3676,16 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>19</v>
@@ -3759,16 +3714,16 @@
         <v>12</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>19</v>
@@ -3797,16 +3752,16 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>19</v>
@@ -3835,16 +3790,16 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>19</v>
@@ -3873,16 +3828,16 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>19</v>
@@ -3911,16 +3866,16 @@
         <v>12</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>19</v>
@@ -3949,16 +3904,16 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>19</v>
@@ -3987,16 +3942,16 @@
         <v>12</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>19</v>
@@ -4025,16 +3980,16 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>19</v>
@@ -4063,16 +4018,16 @@
         <v>12</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>19</v>
@@ -4101,16 +4056,16 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>19</v>
@@ -4139,16 +4094,16 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>19</v>
@@ -4177,16 +4132,16 @@
         <v>12</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>19</v>
@@ -4215,16 +4170,16 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>19</v>
@@ -4253,16 +4208,16 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>19</v>
@@ -4291,16 +4246,16 @@
         <v>12</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>19</v>
@@ -4329,16 +4284,16 @@
         <v>12</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>19</v>
@@ -4367,16 +4322,16 @@
         <v>12</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="E76" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="F76" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="G76" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>19</v>
@@ -4405,13 +4360,13 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="F77" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="G77" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>19</v>
@@ -4440,16 +4395,16 @@
         <v>12</v>
       </c>
       <c r="D78" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="E78" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="F78" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="G78" s="5" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>19</v>
